--- a/administrative_forms/030_counselor_honorarium_submission_form--administrative_forms.xlsx
+++ b/administrative_forms/030_counselor_honorarium_submission_form--administrative_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1166,8 +1166,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'counselor'}</t>
+          <t>counselor</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Counselor'}</t>
+          <t>Counselor</t>
         </is>
       </c>
     </row>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'administrator'}</t>
+          <t>administrator</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Administrator'}</t>
+          <t>Administrator</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'check'}</t>
+          <t>check</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Check'}</t>
+          <t>Check</t>
         </is>
       </c>
     </row>
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'online_payment'}</t>
+          <t>online_payment</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Online Payment'}</t>
+          <t>Online Payment</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'counselor'}</t>
+          <t>counselor</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Counselor'}</t>
+          <t>Counselor</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'administrator'}</t>
+          <t>administrator</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Administrator'}</t>
+          <t>Administrator</t>
         </is>
       </c>
     </row>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'denied'}</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Denied'}</t>
+          <t>Denied</t>
         </is>
       </c>
     </row>
@@ -1365,12 +1365,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1382,12 +1382,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'paid'}</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Paid'}</t>
+          <t>Paid</t>
         </is>
       </c>
     </row>
@@ -1399,12 +1399,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'unpaid'}</t>
+          <t>unpaid</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Unpaid'}</t>
+          <t>Unpaid</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1433,12 +1433,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1450,12 +1450,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'paid'}</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Paid'}</t>
+          <t>Paid</t>
         </is>
       </c>
     </row>
@@ -1484,12 +1484,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'unpaid'}</t>
+          <t>unpaid</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Unpaid'}</t>
+          <t>Unpaid</t>
         </is>
       </c>
     </row>
